--- a/saida/2026-07/relatorio.xlsx
+++ b/saida/2026-07/relatorio.xlsx
@@ -379,6 +379,12 @@
           <tx>
             <strRef>
               <f>'Resumo'!B14</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Faturamento líquido</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -390,13 +396,38 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Resumo'!$A$15:$A$17</f>
-            </numRef>
+              <strCache>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>Centro</v>
+                </pt>
+                <pt idx="1">
+                  <v>Umarizal</v>
+                </pt>
+                <pt idx="2">
+                  <v>Ananindeua</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Resumo'!$B$15:$B$17</f>
+              <numCache>
+                <formatCode>"R$" #,##0.00;[Red]-"R$" #,##0.00</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>46993.38</v>
+                </pt>
+                <pt idx="1">
+                  <v>38845.27</v>
+                </pt>
+                <pt idx="2">
+                  <v>25457.92</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -406,6 +437,12 @@
           <tx>
             <strRef>
               <f>'Resumo'!C14</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Meta</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -417,13 +454,38 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Resumo'!$A$15:$A$17</f>
-            </numRef>
+              <strCache>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>Centro</v>
+                </pt>
+                <pt idx="1">
+                  <v>Umarizal</v>
+                </pt>
+                <pt idx="2">
+                  <v>Ananindeua</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Resumo'!$C$15:$C$17</f>
+              <numCache>
+                <formatCode>"R$" #,##0.00;[Red]-"R$" #,##0.00</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>45000</v>
+                </pt>
+                <pt idx="1">
+                  <v>38000</v>
+                </pt>
+                <pt idx="2">
+                  <v>26000</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -494,6 +556,12 @@
           <tx>
             <strRef>
               <f>'Resumo'!B21</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Faturamento líquido</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -505,13 +573,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Resumo'!$A$22:$A$26</f>
-            </numRef>
+              <strCache>
+                <ptCount val="5"/>
+                <pt idx="0">
+                  <v>Dermatológicos</v>
+                </pt>
+                <pt idx="1">
+                  <v>Cápsulas e suplementos</v>
+                </pt>
+                <pt idx="2">
+                  <v>Veterinários</v>
+                </pt>
+                <pt idx="3">
+                  <v>Florais e homeopatia</v>
+                </pt>
+                <pt idx="4">
+                  <v>Revenda</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Resumo'!$B$22:$B$26</f>
+              <numCache>
+                <formatCode>"R$" #,##0.00;[Red]-"R$" #,##0.00</formatCode>
+                <ptCount val="5"/>
+                <pt idx="0">
+                  <v>50724.72</v>
+                </pt>
+                <pt idx="1">
+                  <v>39361.09</v>
+                </pt>
+                <pt idx="2">
+                  <v>7312.63</v>
+                </pt>
+                <pt idx="3">
+                  <v>7132.33</v>
+                </pt>
+                <pt idx="4">
+                  <v>6765.8</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -579,6 +684,12 @@
           <tx>
             <strRef>
               <f>'Vendas por dia'!C4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Centro</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -592,11 +703,181 @@
           <cat>
             <numRef>
               <f>'Vendas por dia'!$A$5:$A$31</f>
+              <numCache>
+                <formatCode>dd/mm/yyyy</formatCode>
+                <ptCount val="27"/>
+                <pt idx="0">
+                  <v>46204</v>
+                </pt>
+                <pt idx="1">
+                  <v>46205</v>
+                </pt>
+                <pt idx="2">
+                  <v>46206</v>
+                </pt>
+                <pt idx="3">
+                  <v>46207</v>
+                </pt>
+                <pt idx="4">
+                  <v>46209</v>
+                </pt>
+                <pt idx="5">
+                  <v>46210</v>
+                </pt>
+                <pt idx="6">
+                  <v>46211</v>
+                </pt>
+                <pt idx="7">
+                  <v>46212</v>
+                </pt>
+                <pt idx="8">
+                  <v>46213</v>
+                </pt>
+                <pt idx="9">
+                  <v>46214</v>
+                </pt>
+                <pt idx="10">
+                  <v>46216</v>
+                </pt>
+                <pt idx="11">
+                  <v>46217</v>
+                </pt>
+                <pt idx="12">
+                  <v>46218</v>
+                </pt>
+                <pt idx="13">
+                  <v>46219</v>
+                </pt>
+                <pt idx="14">
+                  <v>46220</v>
+                </pt>
+                <pt idx="15">
+                  <v>46221</v>
+                </pt>
+                <pt idx="16">
+                  <v>46223</v>
+                </pt>
+                <pt idx="17">
+                  <v>46224</v>
+                </pt>
+                <pt idx="18">
+                  <v>46225</v>
+                </pt>
+                <pt idx="19">
+                  <v>46226</v>
+                </pt>
+                <pt idx="20">
+                  <v>46227</v>
+                </pt>
+                <pt idx="21">
+                  <v>46228</v>
+                </pt>
+                <pt idx="22">
+                  <v>46230</v>
+                </pt>
+                <pt idx="23">
+                  <v>46231</v>
+                </pt>
+                <pt idx="24">
+                  <v>46232</v>
+                </pt>
+                <pt idx="25">
+                  <v>46233</v>
+                </pt>
+                <pt idx="26">
+                  <v>46234</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Vendas por dia'!$C$5:$C$31</f>
+              <numCache>
+                <formatCode>"R$" #,##0.00;[Red]-"R$" #,##0.00</formatCode>
+                <ptCount val="27"/>
+                <pt idx="0">
+                  <v>1981.03</v>
+                </pt>
+                <pt idx="1">
+                  <v>1424.42</v>
+                </pt>
+                <pt idx="2">
+                  <v>1698.64</v>
+                </pt>
+                <pt idx="3">
+                  <v>1017.54</v>
+                </pt>
+                <pt idx="4">
+                  <v>2432.32</v>
+                </pt>
+                <pt idx="5">
+                  <v>1939.5</v>
+                </pt>
+                <pt idx="6">
+                  <v>2012.85</v>
+                </pt>
+                <pt idx="7">
+                  <v>1411.94</v>
+                </pt>
+                <pt idx="8">
+                  <v>2999.12</v>
+                </pt>
+                <pt idx="9">
+                  <v>1200.07</v>
+                </pt>
+                <pt idx="10">
+                  <v>1256.78</v>
+                </pt>
+                <pt idx="11">
+                  <v>2328.61</v>
+                </pt>
+                <pt idx="12">
+                  <v>1156.07</v>
+                </pt>
+                <pt idx="13">
+                  <v>2335.8</v>
+                </pt>
+                <pt idx="14">
+                  <v>1597.14</v>
+                </pt>
+                <pt idx="15">
+                  <v>1141.92</v>
+                </pt>
+                <pt idx="16">
+                  <v>1249.8</v>
+                </pt>
+                <pt idx="17">
+                  <v>1819.2</v>
+                </pt>
+                <pt idx="18">
+                  <v>1433.58</v>
+                </pt>
+                <pt idx="19">
+                  <v>2190.96</v>
+                </pt>
+                <pt idx="20">
+                  <v>1937.79</v>
+                </pt>
+                <pt idx="21">
+                  <v>1354.85</v>
+                </pt>
+                <pt idx="22">
+                  <v>1871.12</v>
+                </pt>
+                <pt idx="23">
+                  <v>1310.42</v>
+                </pt>
+                <pt idx="24">
+                  <v>1848.44</v>
+                </pt>
+                <pt idx="25">
+                  <v>2161.49</v>
+                </pt>
+                <pt idx="26">
+                  <v>1881.98</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -606,6 +887,12 @@
           <tx>
             <strRef>
               <f>'Vendas por dia'!D4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Umarizal</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -619,11 +906,181 @@
           <cat>
             <numRef>
               <f>'Vendas por dia'!$A$5:$A$31</f>
+              <numCache>
+                <formatCode>dd/mm/yyyy</formatCode>
+                <ptCount val="27"/>
+                <pt idx="0">
+                  <v>46204</v>
+                </pt>
+                <pt idx="1">
+                  <v>46205</v>
+                </pt>
+                <pt idx="2">
+                  <v>46206</v>
+                </pt>
+                <pt idx="3">
+                  <v>46207</v>
+                </pt>
+                <pt idx="4">
+                  <v>46209</v>
+                </pt>
+                <pt idx="5">
+                  <v>46210</v>
+                </pt>
+                <pt idx="6">
+                  <v>46211</v>
+                </pt>
+                <pt idx="7">
+                  <v>46212</v>
+                </pt>
+                <pt idx="8">
+                  <v>46213</v>
+                </pt>
+                <pt idx="9">
+                  <v>46214</v>
+                </pt>
+                <pt idx="10">
+                  <v>46216</v>
+                </pt>
+                <pt idx="11">
+                  <v>46217</v>
+                </pt>
+                <pt idx="12">
+                  <v>46218</v>
+                </pt>
+                <pt idx="13">
+                  <v>46219</v>
+                </pt>
+                <pt idx="14">
+                  <v>46220</v>
+                </pt>
+                <pt idx="15">
+                  <v>46221</v>
+                </pt>
+                <pt idx="16">
+                  <v>46223</v>
+                </pt>
+                <pt idx="17">
+                  <v>46224</v>
+                </pt>
+                <pt idx="18">
+                  <v>46225</v>
+                </pt>
+                <pt idx="19">
+                  <v>46226</v>
+                </pt>
+                <pt idx="20">
+                  <v>46227</v>
+                </pt>
+                <pt idx="21">
+                  <v>46228</v>
+                </pt>
+                <pt idx="22">
+                  <v>46230</v>
+                </pt>
+                <pt idx="23">
+                  <v>46231</v>
+                </pt>
+                <pt idx="24">
+                  <v>46232</v>
+                </pt>
+                <pt idx="25">
+                  <v>46233</v>
+                </pt>
+                <pt idx="26">
+                  <v>46234</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Vendas por dia'!$D$5:$D$31</f>
+              <numCache>
+                <formatCode>"R$" #,##0.00;[Red]-"R$" #,##0.00</formatCode>
+                <ptCount val="27"/>
+                <pt idx="0">
+                  <v>1880.97</v>
+                </pt>
+                <pt idx="1">
+                  <v>1555.63</v>
+                </pt>
+                <pt idx="2">
+                  <v>1263.53</v>
+                </pt>
+                <pt idx="3">
+                  <v>699.88</v>
+                </pt>
+                <pt idx="4">
+                  <v>2099.58</v>
+                </pt>
+                <pt idx="5">
+                  <v>1436.88</v>
+                </pt>
+                <pt idx="6">
+                  <v>1619.9</v>
+                </pt>
+                <pt idx="7">
+                  <v>1398.6</v>
+                </pt>
+                <pt idx="8">
+                  <v>1431.61</v>
+                </pt>
+                <pt idx="9">
+                  <v>959.35</v>
+                </pt>
+                <pt idx="10">
+                  <v>1752.76</v>
+                </pt>
+                <pt idx="11">
+                  <v>1770.34</v>
+                </pt>
+                <pt idx="12">
+                  <v>1464.18</v>
+                </pt>
+                <pt idx="13">
+                  <v>1185.62</v>
+                </pt>
+                <pt idx="14">
+                  <v>1419.62</v>
+                </pt>
+                <pt idx="15">
+                  <v>708.25</v>
+                </pt>
+                <pt idx="16">
+                  <v>1441.13</v>
+                </pt>
+                <pt idx="17">
+                  <v>1719.78</v>
+                </pt>
+                <pt idx="18">
+                  <v>1486.96</v>
+                </pt>
+                <pt idx="19">
+                  <v>1610.97</v>
+                </pt>
+                <pt idx="20">
+                  <v>1489.67</v>
+                </pt>
+                <pt idx="21">
+                  <v>988.62</v>
+                </pt>
+                <pt idx="22">
+                  <v>1618.45</v>
+                </pt>
+                <pt idx="23">
+                  <v>1038.5</v>
+                </pt>
+                <pt idx="24">
+                  <v>1566.75</v>
+                </pt>
+                <pt idx="25">
+                  <v>1802.28</v>
+                </pt>
+                <pt idx="26">
+                  <v>1435.46</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -633,6 +1090,12 @@
           <tx>
             <strRef>
               <f>'Vendas por dia'!E4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Ananindeua</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -646,11 +1109,181 @@
           <cat>
             <numRef>
               <f>'Vendas por dia'!$A$5:$A$31</f>
+              <numCache>
+                <formatCode>dd/mm/yyyy</formatCode>
+                <ptCount val="27"/>
+                <pt idx="0">
+                  <v>46204</v>
+                </pt>
+                <pt idx="1">
+                  <v>46205</v>
+                </pt>
+                <pt idx="2">
+                  <v>46206</v>
+                </pt>
+                <pt idx="3">
+                  <v>46207</v>
+                </pt>
+                <pt idx="4">
+                  <v>46209</v>
+                </pt>
+                <pt idx="5">
+                  <v>46210</v>
+                </pt>
+                <pt idx="6">
+                  <v>46211</v>
+                </pt>
+                <pt idx="7">
+                  <v>46212</v>
+                </pt>
+                <pt idx="8">
+                  <v>46213</v>
+                </pt>
+                <pt idx="9">
+                  <v>46214</v>
+                </pt>
+                <pt idx="10">
+                  <v>46216</v>
+                </pt>
+                <pt idx="11">
+                  <v>46217</v>
+                </pt>
+                <pt idx="12">
+                  <v>46218</v>
+                </pt>
+                <pt idx="13">
+                  <v>46219</v>
+                </pt>
+                <pt idx="14">
+                  <v>46220</v>
+                </pt>
+                <pt idx="15">
+                  <v>46221</v>
+                </pt>
+                <pt idx="16">
+                  <v>46223</v>
+                </pt>
+                <pt idx="17">
+                  <v>46224</v>
+                </pt>
+                <pt idx="18">
+                  <v>46225</v>
+                </pt>
+                <pt idx="19">
+                  <v>46226</v>
+                </pt>
+                <pt idx="20">
+                  <v>46227</v>
+                </pt>
+                <pt idx="21">
+                  <v>46228</v>
+                </pt>
+                <pt idx="22">
+                  <v>46230</v>
+                </pt>
+                <pt idx="23">
+                  <v>46231</v>
+                </pt>
+                <pt idx="24">
+                  <v>46232</v>
+                </pt>
+                <pt idx="25">
+                  <v>46233</v>
+                </pt>
+                <pt idx="26">
+                  <v>46234</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Vendas por dia'!$E$5:$E$31</f>
+              <numCache>
+                <formatCode>"R$" #,##0.00;[Red]-"R$" #,##0.00</formatCode>
+                <ptCount val="27"/>
+                <pt idx="0">
+                  <v>1435.18</v>
+                </pt>
+                <pt idx="1">
+                  <v>840.3</v>
+                </pt>
+                <pt idx="2">
+                  <v>955.16</v>
+                </pt>
+                <pt idx="3">
+                  <v>582.87</v>
+                </pt>
+                <pt idx="4">
+                  <v>890.36</v>
+                </pt>
+                <pt idx="5">
+                  <v>1173.77</v>
+                </pt>
+                <pt idx="6">
+                  <v>750.23</v>
+                </pt>
+                <pt idx="7">
+                  <v>1335.92</v>
+                </pt>
+                <pt idx="8">
+                  <v>752.22</v>
+                </pt>
+                <pt idx="9">
+                  <v>867.45</v>
+                </pt>
+                <pt idx="10">
+                  <v>960.02</v>
+                </pt>
+                <pt idx="11">
+                  <v>1262.05</v>
+                </pt>
+                <pt idx="12">
+                  <v>747.8</v>
+                </pt>
+                <pt idx="13">
+                  <v>975.42</v>
+                </pt>
+                <pt idx="14">
+                  <v>1210.94</v>
+                </pt>
+                <pt idx="15">
+                  <v>708.92</v>
+                </pt>
+                <pt idx="16">
+                  <v>546.5700000000001</v>
+                </pt>
+                <pt idx="17">
+                  <v>1447.69</v>
+                </pt>
+                <pt idx="18">
+                  <v>1167.09</v>
+                </pt>
+                <pt idx="19">
+                  <v>847.33</v>
+                </pt>
+                <pt idx="20">
+                  <v>750.36</v>
+                </pt>
+                <pt idx="21">
+                  <v>591.72</v>
+                </pt>
+                <pt idx="22">
+                  <v>584.59</v>
+                </pt>
+                <pt idx="23">
+                  <v>753.64</v>
+                </pt>
+                <pt idx="24">
+                  <v>893.54</v>
+                </pt>
+                <pt idx="25">
+                  <v>1275.64</v>
+                </pt>
+                <pt idx="26">
+                  <v>1151.14</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -1723,7 +2356,7 @@
       </c>
       <c r="F5" s="31">
         <f>SUM(C5:E5)</f>
-        <v/>
+        <v>5297.18</v>
       </c>
     </row>
     <row r="6">
@@ -1746,7 +2379,7 @@
       </c>
       <c r="F6" s="33">
         <f>SUM(C6:E6)</f>
-        <v/>
+        <v>3820.35</v>
       </c>
     </row>
     <row r="7">
@@ -1769,7 +2402,7 @@
       </c>
       <c r="F7" s="31">
         <f>SUM(C7:E7)</f>
-        <v/>
+        <v>3917.33</v>
       </c>
     </row>
     <row r="8">
@@ -1792,7 +2425,7 @@
       </c>
       <c r="F8" s="33">
         <f>SUM(C8:E8)</f>
-        <v/>
+        <v>2300.29</v>
       </c>
     </row>
     <row r="9">
@@ -1815,7 +2448,7 @@
       </c>
       <c r="F9" s="31">
         <f>SUM(C9:E9)</f>
-        <v/>
+        <v>5422.26</v>
       </c>
     </row>
     <row r="10">
@@ -1838,7 +2471,7 @@
       </c>
       <c r="F10" s="33">
         <f>SUM(C10:E10)</f>
-        <v/>
+        <v>4550.15</v>
       </c>
     </row>
     <row r="11">
@@ -1861,7 +2494,7 @@
       </c>
       <c r="F11" s="31">
         <f>SUM(C11:E11)</f>
-        <v/>
+        <v>4382.98</v>
       </c>
     </row>
     <row r="12">
@@ -1884,7 +2517,7 @@
       </c>
       <c r="F12" s="33">
         <f>SUM(C12:E12)</f>
-        <v/>
+        <v>4146.46</v>
       </c>
     </row>
     <row r="13">
@@ -1907,7 +2540,7 @@
       </c>
       <c r="F13" s="31">
         <f>SUM(C13:E13)</f>
-        <v/>
+        <v>5182.95</v>
       </c>
     </row>
     <row r="14">
@@ -1930,7 +2563,7 @@
       </c>
       <c r="F14" s="33">
         <f>SUM(C14:E14)</f>
-        <v/>
+        <v>3026.87</v>
       </c>
     </row>
     <row r="15">
@@ -1953,7 +2586,7 @@
       </c>
       <c r="F15" s="31">
         <f>SUM(C15:E15)</f>
-        <v/>
+        <v>3969.56</v>
       </c>
     </row>
     <row r="16">
@@ -1976,7 +2609,7 @@
       </c>
       <c r="F16" s="33">
         <f>SUM(C16:E16)</f>
-        <v/>
+        <v>5361.0</v>
       </c>
     </row>
     <row r="17">
@@ -1999,7 +2632,7 @@
       </c>
       <c r="F17" s="31">
         <f>SUM(C17:E17)</f>
-        <v/>
+        <v>3368.05</v>
       </c>
     </row>
     <row r="18">
@@ -2022,7 +2655,7 @@
       </c>
       <c r="F18" s="33">
         <f>SUM(C18:E18)</f>
-        <v/>
+        <v>4496.84</v>
       </c>
     </row>
     <row r="19">
@@ -2045,7 +2678,7 @@
       </c>
       <c r="F19" s="31">
         <f>SUM(C19:E19)</f>
-        <v/>
+        <v>4227.7</v>
       </c>
     </row>
     <row r="20">
@@ -2068,7 +2701,7 @@
       </c>
       <c r="F20" s="33">
         <f>SUM(C20:E20)</f>
-        <v/>
+        <v>2559.09</v>
       </c>
     </row>
     <row r="21">
@@ -2091,7 +2724,7 @@
       </c>
       <c r="F21" s="31">
         <f>SUM(C21:E21)</f>
-        <v/>
+        <v>3237.5</v>
       </c>
     </row>
     <row r="22">
@@ -2114,7 +2747,7 @@
       </c>
       <c r="F22" s="33">
         <f>SUM(C22:E22)</f>
-        <v/>
+        <v>4986.67</v>
       </c>
     </row>
     <row r="23">
@@ -2137,7 +2770,7 @@
       </c>
       <c r="F23" s="31">
         <f>SUM(C23:E23)</f>
-        <v/>
+        <v>4087.63</v>
       </c>
     </row>
     <row r="24">
@@ -2160,7 +2793,7 @@
       </c>
       <c r="F24" s="33">
         <f>SUM(C24:E24)</f>
-        <v/>
+        <v>4649.26</v>
       </c>
     </row>
     <row r="25">
@@ -2183,7 +2816,7 @@
       </c>
       <c r="F25" s="31">
         <f>SUM(C25:E25)</f>
-        <v/>
+        <v>4177.82</v>
       </c>
     </row>
     <row r="26">
@@ -2206,7 +2839,7 @@
       </c>
       <c r="F26" s="33">
         <f>SUM(C26:E26)</f>
-        <v/>
+        <v>2935.19</v>
       </c>
     </row>
     <row r="27">
@@ -2229,7 +2862,7 @@
       </c>
       <c r="F27" s="31">
         <f>SUM(C27:E27)</f>
-        <v/>
+        <v>4074.16</v>
       </c>
     </row>
     <row r="28">
@@ -2252,7 +2885,7 @@
       </c>
       <c r="F28" s="33">
         <f>SUM(C28:E28)</f>
-        <v/>
+        <v>3102.56</v>
       </c>
     </row>
     <row r="29">
@@ -2275,7 +2908,7 @@
       </c>
       <c r="F29" s="31">
         <f>SUM(C29:E29)</f>
-        <v/>
+        <v>4308.73</v>
       </c>
     </row>
     <row r="30">
@@ -2298,7 +2931,7 @@
       </c>
       <c r="F30" s="33">
         <f>SUM(C30:E30)</f>
-        <v/>
+        <v>5239.41</v>
       </c>
     </row>
     <row r="31">
@@ -2321,7 +2954,7 @@
       </c>
       <c r="F31" s="31">
         <f>SUM(C31:E31)</f>
-        <v/>
+        <v>4468.58</v>
       </c>
     </row>
     <row r="32">
@@ -2333,19 +2966,19 @@
       <c r="B32" s="23" t="n"/>
       <c r="C32" s="24">
         <f>SUM(C5:C31)</f>
-        <v/>
+        <v>46993.38</v>
       </c>
       <c r="D32" s="24">
         <f>SUM(D5:D31)</f>
-        <v/>
+        <v>38845.27</v>
       </c>
       <c r="E32" s="24">
         <f>SUM(E5:E31)</f>
-        <v/>
+        <v>25457.92</v>
       </c>
       <c r="F32" s="24">
         <f>SUM(F5:F31)</f>
-        <v/>
+        <v>111296.57</v>
       </c>
     </row>
   </sheetData>
